--- a/.dist/study/reports/artifacts_v2/combined/Combined_2026-09-14.xlsx
+++ b/.dist/study/reports/artifacts_v2/combined/Combined_2026-09-14.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,8 +37,12 @@
       <color rgb="000563C1"/>
       <u val="single"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+    </font>
   </fonts>
-  <fills count="95">
+  <fills count="96">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +59,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF3B0"/>
         <bgColor rgb="00FFF3B0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008EA9DB"/>
+        <bgColor rgb="008EA9DB"/>
       </patternFill>
     </fill>
     <fill>
@@ -616,14 +626,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -635,6 +644,7 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -714,6 +724,7 @@
     <xf numFmtId="0" fontId="0" fillId="92" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="93" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="94" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="95" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -7793,7 +7804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7809,6 +7820,10 @@
           <t>All Projects</t>
         </is>
       </c>
+      <c r="B1" s="5" t="n"/>
+      <c r="C1" s="5" t="n"/>
+      <c r="D1" s="5" t="n"/>
+      <c r="E1" s="5" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -8022,181 +8037,139 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="17" t="n">
         <v>257</v>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="17" t="n">
         <v>257</v>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Chart</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>ODC Type</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr">
         <is>
           <t>Pre-fix Count</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>Pre-fix %</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr">
+      <c r="D16" s="1" t="inlineStr">
         <is>
           <t>Post-fix Count</t>
         </is>
       </c>
-      <c r="E14" s="1" t="inlineStr">
+      <c r="E16" s="1" t="inlineStr">
         <is>
           <t>Post-fix %</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>19.2%</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>19.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Assignment/Initialization</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>6</v>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>23.1%</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>19.2%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Checking</t>
+          <t>Algorithm/Method</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>57.7%</t>
+        <v>5</v>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15</v>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>57.7%</t>
+        <v>5</v>
+      </c>
+      <c r="E17" s="18" t="inlineStr">
+        <is>
+          <t>19.2%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Timing/Serialization</t>
+          <t>Assignment/Initialization</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+        <v>6</v>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+        <v>5</v>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
+        <is>
+          <t>19.2%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Function/Class/Object</t>
+          <t>Checking</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+        <v>15</v>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>3.8%</t>
+        <v>15</v>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>57.7%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Interface/O-O Messages</t>
+          <t>Timing/Serialization</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -8219,7 +8192,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Function/Class/Object</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -8231,890 +8204,799 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+        <v>1</v>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>3.8%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Interface/O-O Messages</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B25" s="17" t="n">
         <v>26</v>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="D23" s="5" t="n">
+      <c r="D25" s="17" t="n">
         <v>26</v>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Lang</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>ODC Type</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
+      <c r="B30" s="1" t="inlineStr">
         <is>
           <t>Pre-fix Count</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>Pre-fix %</t>
         </is>
       </c>
-      <c r="D26" s="1" t="inlineStr">
+      <c r="D30" s="1" t="inlineStr">
         <is>
           <t>Post-fix Count</t>
         </is>
       </c>
-      <c r="E26" s="1" t="inlineStr">
+      <c r="E30" s="1" t="inlineStr">
         <is>
           <t>Post-fix %</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>22</v>
-      </c>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>36.1%</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>21</v>
-      </c>
-      <c r="E27" s="20" t="inlineStr">
-        <is>
-          <t>34.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Assignment/Initialization</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>5</v>
-      </c>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>8.2%</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>4</v>
-      </c>
-      <c r="E28" s="22" t="inlineStr">
-        <is>
-          <t>6.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>33</v>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>54.1%</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>33</v>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>54.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Timing/Serialization</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Function/Class/Object</t>
+          <t>Algorithm/Method</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="23" t="inlineStr">
-        <is>
-          <t>1.6%</t>
+        <v>22</v>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="23" t="inlineStr">
-        <is>
-          <t>1.6%</t>
+        <v>21</v>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>34.4%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Interface/O-O Messages</t>
+          <t>Assignment/Initialization</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+        <v>5</v>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>6.6%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Checking</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+        <v>33</v>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="23" t="inlineStr">
-        <is>
-          <t>1.6%</t>
+        <v>33</v>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>54.1%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Timing/Serialization</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Function/Class/Object</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Interface/O-O Messages</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="24" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="inlineStr">
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B39" s="17" t="n">
         <v>61</v>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C39" s="17" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="D35" s="5" t="n">
+      <c r="D39" s="17" t="n">
         <v>61</v>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E39" s="17" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
         <is>
           <t>ODC Type</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
+      <c r="B44" s="1" t="inlineStr">
         <is>
           <t>Pre-fix Count</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>Pre-fix %</t>
         </is>
       </c>
-      <c r="D38" s="1" t="inlineStr">
+      <c r="D44" s="1" t="inlineStr">
         <is>
           <t>Post-fix Count</t>
         </is>
       </c>
-      <c r="E38" s="1" t="inlineStr">
+      <c r="E44" s="1" t="inlineStr">
         <is>
           <t>Post-fix %</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>53</v>
-      </c>
-      <c r="C39" s="10" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>46</v>
-      </c>
-      <c r="E39" s="24" t="inlineStr">
-        <is>
-          <t>43.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Assignment/Initialization</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>9</v>
-      </c>
-      <c r="C40" s="25" t="inlineStr">
-        <is>
-          <t>8.5%</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>14</v>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>13.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>42</v>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>39.6%</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>41</v>
-      </c>
-      <c r="E41" s="26" t="inlineStr">
-        <is>
-          <t>38.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Timing/Serialization</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Function/Class/Object</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Interface/O-O Messages</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" s="15" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>3</v>
-      </c>
-      <c r="E44" s="27" t="inlineStr">
-        <is>
-          <t>2.8%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Algorithm/Method</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" s="15" t="inlineStr">
-        <is>
-          <t>0.9%</t>
+        <v>53</v>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
-      </c>
-      <c r="E45" s="28" t="inlineStr">
-        <is>
-          <t>1.9%</t>
+        <v>46</v>
+      </c>
+      <c r="E45" s="25" t="inlineStr">
+        <is>
+          <t>43.4%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Assignment/Initialization</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>8.5%</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>14</v>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>13.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>42</v>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>39.6%</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>41</v>
+      </c>
+      <c r="E47" s="27" t="inlineStr">
+        <is>
+          <t>38.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Timing/Serialization</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="inlineStr">
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="n">
-        <v>106</v>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>106</v>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Mockito</t>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Function/Class/Object</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>ODC Type</t>
-        </is>
-      </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>Pre-fix Count</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>Pre-fix %</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>Post-fix Count</t>
-        </is>
-      </c>
-      <c r="E50" s="1" t="inlineStr">
-        <is>
-          <t>Post-fix %</t>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Interface/O-O Messages</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" s="28" t="inlineStr">
+        <is>
+          <t>2.8%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Algorithm/Method</t>
+          <t>Relationship</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>17</v>
-      </c>
-      <c r="C51" s="10" t="inlineStr">
-        <is>
-          <t>44.7%</t>
+        <v>1</v>
+      </c>
+      <c r="C51" s="15" t="inlineStr">
+        <is>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E51" s="29" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>1.9%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="n">
+        <v>106</v>
+      </c>
+      <c r="C53" s="17" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="D53" s="17" t="n">
+        <v>106</v>
+      </c>
+      <c r="E53" s="17" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Mockito</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n"/>
+      <c r="C57" s="5" t="n"/>
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="5" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>ODC Type</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>Pre-fix Count</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>Pre-fix %</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="inlineStr">
+        <is>
+          <t>Post-fix Count</t>
+        </is>
+      </c>
+      <c r="E58" s="1" t="inlineStr">
+        <is>
+          <t>Post-fix %</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>17</v>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>44.7%</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>14</v>
+      </c>
+      <c r="E59" s="30" t="inlineStr">
+        <is>
+          <t>36.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>Assignment/Initialization</t>
         </is>
       </c>
-      <c r="B52" t="n">
+      <c r="B60" t="n">
         <v>4</v>
       </c>
-      <c r="C52" s="30" t="inlineStr">
+      <c r="C60" s="31" t="inlineStr">
         <is>
           <t>10.5%</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D60" t="n">
         <v>6</v>
       </c>
-      <c r="E52" s="31" t="inlineStr">
+      <c r="E60" s="32" t="inlineStr">
         <is>
           <t>15.8%</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
         <v>16</v>
       </c>
-      <c r="C53" s="32" t="inlineStr">
+      <c r="C61" s="33" t="inlineStr">
         <is>
           <t>42.1%</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D61" t="n">
         <v>12</v>
       </c>
-      <c r="E53" s="33" t="inlineStr">
+      <c r="E61" s="34" t="inlineStr">
         <is>
           <t>31.6%</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>Timing/Serialization</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>0</v>
-      </c>
-      <c r="C54" t="inlineStr">
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="inlineStr">
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="inlineStr">
         <is>
           <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Function/Class/Object</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>0</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="27" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Interface/O-O Messages</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>0</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" s="27" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Relationship</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" s="27" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>4</v>
-      </c>
-      <c r="E57" s="30" t="inlineStr">
-        <is>
-          <t>10.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="inlineStr">
-        <is>
-          <t>ODC Type</t>
-        </is>
-      </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>Pre-fix Count</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>Pre-fix %</t>
-        </is>
-      </c>
-      <c r="D62" s="1" t="inlineStr">
-        <is>
-          <t>Post-fix Count</t>
-        </is>
-      </c>
-      <c r="E62" s="1" t="inlineStr">
-        <is>
-          <t>Post-fix %</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Algorithm/Method</t>
+          <t>Function/Class/Object</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>9</v>
-      </c>
-      <c r="C63" s="34" t="inlineStr">
-        <is>
-          <t>34.6%</t>
+        <v>0</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10</v>
-      </c>
-      <c r="E63" s="19" t="inlineStr">
-        <is>
-          <t>38.5%</t>
+        <v>1</v>
+      </c>
+      <c r="E63" s="28" t="inlineStr">
+        <is>
+          <t>2.6%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Assignment/Initialization</t>
+          <t>Interface/O-O Messages</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2</v>
-      </c>
-      <c r="C64" s="35" t="inlineStr">
-        <is>
-          <t>7.7%</t>
+        <v>0</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>3</v>
-      </c>
-      <c r="E64" s="36" t="inlineStr">
-        <is>
-          <t>11.5%</t>
+        <v>1</v>
+      </c>
+      <c r="E64" s="28" t="inlineStr">
+        <is>
+          <t>2.6%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Checking</t>
+          <t>Relationship</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>15</v>
-      </c>
-      <c r="C65" s="10" t="inlineStr">
-        <is>
-          <t>57.7%</t>
+        <v>1</v>
+      </c>
+      <c r="C65" s="28" t="inlineStr">
+        <is>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12</v>
-      </c>
-      <c r="E65" s="37" t="inlineStr">
-        <is>
-          <t>46.2%</t>
+        <v>4</v>
+      </c>
+      <c r="E65" s="31" t="inlineStr">
+        <is>
+          <t>10.5%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Timing/Serialization</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -9135,115 +9017,268 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Function/Class/Object</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>0</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Interface/O-O Messages</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>0</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Relationship</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>0</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" s="16" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>0</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B67" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="C67" s="17" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="D67" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="E67" s="17" t="inlineStr">
+        <is>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n"/>
+      <c r="C71" s="5" t="n"/>
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="5" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>ODC Type</t>
+        </is>
+      </c>
+      <c r="B72" s="1" t="inlineStr">
+        <is>
+          <t>Pre-fix Count</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>Pre-fix %</t>
+        </is>
+      </c>
+      <c r="D72" s="1" t="inlineStr">
+        <is>
+          <t>Post-fix Count</t>
+        </is>
+      </c>
+      <c r="E72" s="1" t="inlineStr">
+        <is>
+          <t>Post-fix %</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>9</v>
+      </c>
+      <c r="C73" s="35" t="inlineStr">
+        <is>
+          <t>34.6%</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" s="20" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Assignment/Initialization</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>2</v>
+      </c>
+      <c r="C74" s="36" t="inlineStr">
+        <is>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>3</v>
+      </c>
+      <c r="E74" s="37" t="inlineStr">
+        <is>
+          <t>11.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>15</v>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>57.7%</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>12</v>
+      </c>
+      <c r="E75" s="38" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Timing/Serialization</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Function/Class/Object</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Interface/O-O Messages</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="16" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="17" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B71" s="5" t="n">
+      <c r="B81" s="17" t="n">
         <v>26</v>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C81" s="17" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="D71" s="5" t="n">
+      <c r="D81" s="17" t="n">
         <v>26</v>
       </c>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="E81" s="17" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -9260,7 +9295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9280,6 +9315,14 @@
           <t>All Projects</t>
         </is>
       </c>
+      <c r="B1" s="5" t="n"/>
+      <c r="C1" s="5" t="n"/>
+      <c r="D1" s="5" t="n"/>
+      <c r="E1" s="5" t="n"/>
+      <c r="F1" s="5" t="n"/>
+      <c r="G1" s="5" t="n"/>
+      <c r="H1" s="5" t="n"/>
+      <c r="I1" s="5" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -9334,25 +9377,25 @@
           <t>Algorithm/Method</t>
         </is>
       </c>
-      <c r="B3" s="38" t="n">
+      <c r="B3" s="39" t="n">
         <v>76</v>
       </c>
-      <c r="C3" s="39" t="n">
+      <c r="C3" s="40" t="n">
         <v>9</v>
       </c>
-      <c r="D3" s="40" t="n">
+      <c r="D3" s="41" t="n">
         <v>15</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="41" t="n">
+      <c r="F3" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="G3" s="27" t="n">
+      <c r="G3" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="42" t="n">
+      <c r="H3" s="43" t="n">
         <v>3</v>
       </c>
       <c r="I3" t="n">
@@ -9365,13 +9408,13 @@
           <t>Assignment/Initialization</t>
         </is>
       </c>
-      <c r="B4" s="41" t="n">
+      <c r="B4" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="43" t="n">
+      <c r="C4" s="44" t="n">
         <v>17</v>
       </c>
-      <c r="D4" s="41" t="n">
+      <c r="D4" s="42" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
@@ -9380,10 +9423,10 @@
       <c r="F4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="41" t="n">
+      <c r="G4" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="H4" s="42" t="n">
+      <c r="H4" s="43" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
@@ -9399,22 +9442,22 @@
       <c r="B5" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="C5" s="44" t="n">
+      <c r="C5" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="45" t="n">
+      <c r="D5" s="46" t="n">
         <v>95</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="27" t="n">
+      <c r="F5" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="41" t="n">
+      <c r="G5" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="27" t="n">
+      <c r="H5" s="28" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
@@ -9461,7 +9504,7 @@
       <c r="B7" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
@@ -9495,7 +9538,7 @@
       <c r="C8" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="27" t="n">
+      <c r="D8" s="28" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
@@ -9520,7 +9563,7 @@
           <t>Relationship</t>
         </is>
       </c>
-      <c r="B9" s="27" t="n">
+      <c r="B9" s="28" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
@@ -9538,7 +9581,7 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="46" t="n">
+      <c r="H9" s="47" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
@@ -9576,122 +9619,99 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>Agreement Rate</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>189/257</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>73.5%</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Chart</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Pre-fix \ Post-fix</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>Assignment/Initialization</t>
         </is>
       </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
         <is>
           <t>Timing/Serialization</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="F16" s="1" t="inlineStr">
         <is>
           <t>Function/Class/Object</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>Interface/O-O Messages</t>
         </is>
       </c>
-      <c r="H15" s="1" t="inlineStr">
+      <c r="H16" s="1" t="inlineStr">
         <is>
           <t>Relationship</t>
         </is>
       </c>
-      <c r="I15" s="1" t="inlineStr">
+      <c r="I16" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="B16" s="47" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Assignment/Initialization</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="n">
-        <v>2</v>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="B17" s="48" t="n">
+        <v>3</v>
       </c>
       <c r="C17" s="49" t="n">
-        <v>4</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D17" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -9712,23 +9732,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="45" t="n">
-        <v>14</v>
+          <t>Assignment/Initialization</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="48" t="n">
-        <v>1</v>
+      <c r="F18" t="n">
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -9743,7 +9763,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Timing/Serialization</t>
+          <t>Checking</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -9752,14 +9772,14 @@
       <c r="C19" t="n">
         <v>0</v>
       </c>
-      <c r="D19" t="n">
-        <v>0</v>
+      <c r="D19" s="46" t="n">
+        <v>14</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
+      <c r="F19" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -9774,7 +9794,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Function/Class/Object</t>
+          <t>Timing/Serialization</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -9805,7 +9825,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Interface/O-O Messages</t>
+          <t>Function/Class/Object</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -9836,7 +9856,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Interface/O-O Messages</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -9867,31 +9887,62 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9912,145 +9963,91 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Lang</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>Pre-fix \ Post-fix</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>Assignment/Initialization</t>
         </is>
       </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="E28" s="1" t="inlineStr">
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
         <is>
           <t>Timing/Serialization</t>
         </is>
       </c>
-      <c r="F28" s="1" t="inlineStr">
+      <c r="F30" s="1" t="inlineStr">
         <is>
           <t>Function/Class/Object</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
+      <c r="G30" s="1" t="inlineStr">
         <is>
           <t>Interface/O-O Messages</t>
         </is>
       </c>
-      <c r="H28" s="1" t="inlineStr">
+      <c r="H30" s="1" t="inlineStr">
         <is>
           <t>Relationship</t>
         </is>
       </c>
-      <c r="I28" s="1" t="inlineStr">
+      <c r="I30" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="B29" s="50" t="n">
-        <v>16</v>
-      </c>
-      <c r="C29" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="37" t="n">
-        <v>4</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Assignment/Initialization</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="D30" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="45" t="n">
-        <v>27</v>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="B31" s="51" t="n">
+        <v>16</v>
+      </c>
+      <c r="C31" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="38" t="n">
+        <v>4</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="36" t="n">
+      <c r="F31" s="37" t="n">
         <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -10062,17 +10059,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Timing/Serialization</t>
+          <t>Assignment/Initialization</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
+      <c r="C32" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -10083,8 +10080,8 @@
       <c r="G32" t="n">
         <v>0</v>
       </c>
-      <c r="H32" t="n">
-        <v>0</v>
+      <c r="H32" s="37" t="n">
+        <v>1</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -10093,26 +10090,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Function/Class/Object</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="36" t="n">
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="46" t="n">
+        <v>27</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="37" t="n">
         <v>1</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -10124,7 +10121,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Interface/O-O Messages</t>
+          <t>Timing/Serialization</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -10155,14 +10152,14 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Function/Class/Object</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>0</v>
       </c>
-      <c r="C35" t="n">
-        <v>0</v>
+      <c r="C35" s="37" t="n">
+        <v>1</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -10186,212 +10183,189 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Interface/O-O Messages</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
         <is>
           <t>Agreement Rate</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
+      <c r="B39" s="1" t="inlineStr">
         <is>
           <t>45/61</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>73.8%</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
         <is>
           <t>Pre-fix \ Post-fix</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>Assignment/Initialization</t>
         </is>
       </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="inlineStr">
         <is>
           <t>Timing/Serialization</t>
         </is>
       </c>
-      <c r="F41" s="1" t="inlineStr">
+      <c r="F44" s="1" t="inlineStr">
         <is>
           <t>Function/Class/Object</t>
         </is>
       </c>
-      <c r="G41" s="1" t="inlineStr">
+      <c r="G44" s="1" t="inlineStr">
         <is>
           <t>Interface/O-O Messages</t>
         </is>
       </c>
-      <c r="H41" s="1" t="inlineStr">
+      <c r="H44" s="1" t="inlineStr">
         <is>
           <t>Relationship</t>
         </is>
       </c>
-      <c r="I41" s="1" t="inlineStr">
+      <c r="I44" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="B42" s="45" t="n">
-        <v>40</v>
-      </c>
-      <c r="C42" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="D42" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Assignment/Initialization</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" s="53" t="n">
-        <v>6</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="H43" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="B44" s="54" t="n">
-        <v>5</v>
-      </c>
-      <c r="C44" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D44" s="55" t="n">
-        <v>34</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Timing/Serialization</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="B45" s="46" t="n">
+        <v>40</v>
+      </c>
+      <c r="C45" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -10402,8 +10376,8 @@
       <c r="G45" t="n">
         <v>0</v>
       </c>
-      <c r="H45" t="n">
-        <v>0</v>
+      <c r="H45" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -10412,14 +10386,14 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Function/Class/Object</t>
+          <t>Assignment/Initialization</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>0</v>
       </c>
-      <c r="C46" t="n">
-        <v>0</v>
+      <c r="C46" s="54" t="n">
+        <v>6</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -10430,11 +10404,11 @@
       <c r="F46" t="n">
         <v>0</v>
       </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
+      <c r="G46" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" s="53" t="n">
+        <v>1</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -10443,26 +10417,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Interface/O-O Messages</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="52" t="n">
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="B47" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="C47" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" s="56" t="n">
+        <v>34</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="53" t="n">
         <v>1</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -10474,11 +10448,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Relationship</t>
-        </is>
-      </c>
-      <c r="B48" s="52" t="n">
-        <v>1</v>
+          <t>Timing/Serialization</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -10505,255 +10479,232 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>Function/Class/Object</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Interface/O-O Messages</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="B51" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
         <is>
           <t>Agreement Rate</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
+      <c r="B53" s="1" t="inlineStr">
         <is>
           <t>80/106</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>75.5%</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>Mockito</t>
         </is>
       </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
+      <c r="B57" s="5" t="n"/>
+      <c r="C57" s="5" t="n"/>
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="5" t="n"/>
+      <c r="I57" s="5" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
         <is>
           <t>Pre-fix \ Post-fix</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>Assignment/Initialization</t>
         </is>
       </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="E54" s="1" t="inlineStr">
+      <c r="D58" s="1" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="E58" s="1" t="inlineStr">
         <is>
           <t>Timing/Serialization</t>
         </is>
       </c>
-      <c r="F54" s="1" t="inlineStr">
+      <c r="F58" s="1" t="inlineStr">
         <is>
           <t>Function/Class/Object</t>
         </is>
       </c>
-      <c r="G54" s="1" t="inlineStr">
+      <c r="G58" s="1" t="inlineStr">
         <is>
           <t>Interface/O-O Messages</t>
         </is>
       </c>
-      <c r="H54" s="1" t="inlineStr">
+      <c r="H58" s="1" t="inlineStr">
         <is>
           <t>Relationship</t>
         </is>
       </c>
-      <c r="I54" s="1" t="inlineStr">
+      <c r="I58" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="B55" s="45" t="n">
-        <v>11</v>
-      </c>
-      <c r="C55" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Assignment/Initialization</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>0</v>
-      </c>
-      <c r="C56" s="56" t="n">
-        <v>3</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="B57" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C57" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D57" s="57" t="n">
-        <v>10</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Timing/Serialization</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Function/Class/Object</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>0</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0</v>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="B59" s="46" t="n">
+        <v>11</v>
+      </c>
+      <c r="C59" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
+      <c r="F59" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -10762,14 +10713,14 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Interface/O-O Messages</t>
+          <t>Assignment/Initialization</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>0</v>
       </c>
-      <c r="C60" t="n">
-        <v>0</v>
+      <c r="C60" s="57" t="n">
+        <v>3</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -10783,8 +10734,8 @@
       <c r="G60" t="n">
         <v>0</v>
       </c>
-      <c r="H60" t="n">
-        <v>0</v>
+      <c r="H60" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
@@ -10793,17 +10744,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Relationship</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>0</v>
-      </c>
-      <c r="C61" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" t="n">
-        <v>0</v>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C61" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" s="58" t="n">
+        <v>10</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -10814,7 +10765,7 @@
       <c r="G61" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="58" t="n">
+      <c r="H61" s="18" t="n">
         <v>1</v>
       </c>
       <c r="I61" t="n">
@@ -10824,274 +10775,251 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>Timing/Serialization</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Function/Class/Object</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Interface/O-O Messages</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B62" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr">
-        <is>
-          <t>Agreement Rate</t>
-        </is>
-      </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>25/38</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>65.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
+          <t>Agreement Rate</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>25/38</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>65.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n"/>
+      <c r="C71" s="5" t="n"/>
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="n"/>
+      <c r="G71" s="5" t="n"/>
+      <c r="H71" s="5" t="n"/>
+      <c r="I71" s="5" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
           <t>Pre-fix \ Post-fix</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="B72" s="1" t="inlineStr">
+        <is>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>Assignment/Initialization</t>
         </is>
       </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="E67" s="1" t="inlineStr">
+      <c r="D72" s="1" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="E72" s="1" t="inlineStr">
         <is>
           <t>Timing/Serialization</t>
         </is>
       </c>
-      <c r="F67" s="1" t="inlineStr">
+      <c r="F72" s="1" t="inlineStr">
         <is>
           <t>Function/Class/Object</t>
         </is>
       </c>
-      <c r="G67" s="1" t="inlineStr">
+      <c r="G72" s="1" t="inlineStr">
         <is>
           <t>Interface/O-O Messages</t>
         </is>
       </c>
-      <c r="H67" s="1" t="inlineStr">
+      <c r="H72" s="1" t="inlineStr">
         <is>
           <t>Relationship</t>
         </is>
       </c>
-      <c r="I67" s="1" t="inlineStr">
+      <c r="I72" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="B68" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="C68" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="60" t="n">
-        <v>1</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Assignment/Initialization</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>0</v>
-      </c>
-      <c r="C69" s="61" t="n">
-        <v>2</v>
-      </c>
-      <c r="D69" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="B70" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="C70" s="60" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" s="45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Timing/Serialization</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Function/Class/Object</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>0</v>
-      </c>
-      <c r="C72" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Interface/O-O Messages</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>0</v>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="B73" s="60" t="n">
+        <v>6</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
-      <c r="D73" t="n">
-        <v>0</v>
+      <c r="D73" s="49" t="n">
+        <v>2</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -11102,8 +11030,8 @@
       <c r="G73" t="n">
         <v>0</v>
       </c>
-      <c r="H73" t="n">
-        <v>0</v>
+      <c r="H73" s="61" t="n">
+        <v>1</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
@@ -11112,14 +11040,14 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Assignment/Initialization</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>0</v>
       </c>
-      <c r="C74" t="n">
-        <v>0</v>
+      <c r="C74" s="62" t="n">
+        <v>2</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -11143,46 +11071,201 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C75" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Timing/Serialization</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Function/Class/Object</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Interface/O-O Messages</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B75" t="n">
-        <v>0</v>
-      </c>
-      <c r="C75" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr">
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
         <is>
           <t>Agreement Rate</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
+      <c r="B81" s="1" t="inlineStr">
         <is>
           <t>18/26</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>69.2%</t>
         </is>
@@ -18963,7 +19046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -18983,6 +19066,14 @@
           <t>All Projects</t>
         </is>
       </c>
+      <c r="B1" s="5" t="n"/>
+      <c r="C1" s="5" t="n"/>
+      <c r="D1" s="5" t="n"/>
+      <c r="E1" s="5" t="n"/>
+      <c r="F1" s="5" t="n"/>
+      <c r="G1" s="5" t="n"/>
+      <c r="H1" s="5" t="n"/>
+      <c r="I1" s="5" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -19037,13 +19128,13 @@
           <t>Algorithm/Method</t>
         </is>
       </c>
-      <c r="B3" s="45" t="n">
+      <c r="B3" s="46" t="n">
         <v>94</v>
       </c>
-      <c r="C3" s="62" t="n">
+      <c r="C3" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="63" t="n">
+      <c r="D3" s="64" t="n">
         <v>5</v>
       </c>
       <c r="E3" t="n">
@@ -19055,7 +19146,7 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="62" t="n">
+      <c r="H3" s="63" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
@@ -19068,10 +19159,10 @@
           <t>Assignment/Initialization</t>
         </is>
       </c>
-      <c r="B4" s="64" t="n">
+      <c r="B4" s="65" t="n">
         <v>16</v>
       </c>
-      <c r="C4" s="65" t="n">
+      <c r="C4" s="66" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
@@ -19080,13 +19171,13 @@
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="66" t="n">
+      <c r="F4" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="66" t="n">
+      <c r="G4" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="62" t="n">
+      <c r="H4" s="63" t="n">
         <v>2</v>
       </c>
       <c r="I4" t="n">
@@ -19102,19 +19193,19 @@
       <c r="B5" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="C5" s="66" t="n">
+      <c r="C5" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="67" t="n">
+      <c r="D5" s="68" t="n">
         <v>73</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="66" t="n">
+      <c r="F5" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="66" t="n">
+      <c r="G5" s="67" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
@@ -19173,7 +19264,7 @@
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="46" t="n">
+      <c r="F7" s="47" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
@@ -19198,7 +19289,7 @@
       <c r="C8" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="66" t="n">
+      <c r="D8" s="67" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
@@ -19223,7 +19314,7 @@
           <t>Relationship</t>
         </is>
       </c>
-      <c r="B9" s="66" t="n">
+      <c r="B9" s="67" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
@@ -19241,7 +19332,7 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="46" t="n">
+      <c r="H9" s="47" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
@@ -19279,119 +19370,96 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>Agreement Rate</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>175/257</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>68.1%</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Chart</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Scientific \ Few</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>Assignment/Initialization</t>
         </is>
       </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
         <is>
           <t>Timing/Serialization</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="F16" s="1" t="inlineStr">
         <is>
           <t>Function/Class/Object</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>Interface/O-O Messages</t>
         </is>
       </c>
-      <c r="H15" s="1" t="inlineStr">
+      <c r="H16" s="1" t="inlineStr">
         <is>
           <t>Relationship</t>
         </is>
       </c>
-      <c r="I15" s="1" t="inlineStr">
+      <c r="I16" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="B16" s="68" t="n">
-        <v>4</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="60" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Assignment/Initialization</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="n">
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="B17" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="C17" s="69" t="n">
-        <v>1</v>
+      <c r="C17" t="n">
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -19405,7 +19473,7 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="60" t="n">
+      <c r="H17" s="61" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="n">
@@ -19415,17 +19483,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="B18" s="70" t="n">
-        <v>3</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="45" t="n">
-        <v>12</v>
+          <t>Assignment/Initialization</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -19436,8 +19504,8 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
+      <c r="H18" s="61" t="n">
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -19446,17 +19514,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Timing/Serialization</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="B19" s="71" t="n">
+        <v>3</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
-      <c r="D19" t="n">
-        <v>0</v>
+      <c r="D19" s="46" t="n">
+        <v>12</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -19477,7 +19545,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Function/Class/Object</t>
+          <t>Timing/Serialization</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -19508,7 +19576,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Interface/O-O Messages</t>
+          <t>Function/Class/Object</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -19539,7 +19607,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Interface/O-O Messages</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -19570,31 +19638,62 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19615,136 +19714,82 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Lang</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>Scientific \ Few</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>Assignment/Initialization</t>
         </is>
       </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="E28" s="1" t="inlineStr">
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
         <is>
           <t>Timing/Serialization</t>
         </is>
       </c>
-      <c r="F28" s="1" t="inlineStr">
+      <c r="F30" s="1" t="inlineStr">
         <is>
           <t>Function/Class/Object</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
+      <c r="G30" s="1" t="inlineStr">
         <is>
           <t>Interface/O-O Messages</t>
         </is>
       </c>
-      <c r="H28" s="1" t="inlineStr">
+      <c r="H30" s="1" t="inlineStr">
         <is>
           <t>Relationship</t>
         </is>
       </c>
-      <c r="I28" s="1" t="inlineStr">
+      <c r="I30" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="B29" s="45" t="n">
-        <v>22</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Assignment/Initialization</t>
-        </is>
-      </c>
-      <c r="B30" s="71" t="n">
-        <v>4</v>
-      </c>
-      <c r="C30" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="n">
-        <v>15</v>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="B31" s="46" t="n">
+        <v>22</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="73" t="n">
-        <v>18</v>
+      <c r="D31" t="n">
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -19765,14 +19810,14 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Timing/Serialization</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0</v>
+          <t>Assignment/Initialization</t>
+        </is>
+      </c>
+      <c r="B32" s="72" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" s="73" t="n">
+        <v>1</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -19796,23 +19841,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Function/Class/Object</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n">
+        <v>15</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
-      <c r="D33" t="n">
-        <v>0</v>
+      <c r="D33" s="74" t="n">
+        <v>18</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
-      <c r="F33" s="72" t="n">
-        <v>1</v>
+      <c r="F33" t="n">
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -19827,7 +19872,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Interface/O-O Messages</t>
+          <t>Timing/Serialization</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -19858,7 +19903,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Function/Class/Object</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -19873,8 +19918,8 @@
       <c r="E35" t="n">
         <v>0</v>
       </c>
-      <c r="F35" t="n">
-        <v>0</v>
+      <c r="F35" s="73" t="n">
+        <v>1</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -19889,212 +19934,189 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Interface/O-O Messages</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
         <is>
           <t>Agreement Rate</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
+      <c r="B39" s="1" t="inlineStr">
         <is>
           <t>42/61</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>68.9%</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
         <is>
           <t>Scientific \ Few</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>Assignment/Initialization</t>
         </is>
       </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="inlineStr">
         <is>
           <t>Timing/Serialization</t>
         </is>
       </c>
-      <c r="F41" s="1" t="inlineStr">
+      <c r="F44" s="1" t="inlineStr">
         <is>
           <t>Function/Class/Object</t>
         </is>
       </c>
-      <c r="G41" s="1" t="inlineStr">
+      <c r="G44" s="1" t="inlineStr">
         <is>
           <t>Interface/O-O Messages</t>
         </is>
       </c>
-      <c r="H41" s="1" t="inlineStr">
+      <c r="H44" s="1" t="inlineStr">
         <is>
           <t>Relationship</t>
         </is>
       </c>
-      <c r="I41" s="1" t="inlineStr">
+      <c r="I44" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="B42" s="45" t="n">
-        <v>48</v>
-      </c>
-      <c r="C42" s="74" t="n">
-        <v>2</v>
-      </c>
-      <c r="D42" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Assignment/Initialization</t>
-        </is>
-      </c>
-      <c r="B43" s="64" t="n">
-        <v>5</v>
-      </c>
-      <c r="C43" s="75" t="n">
-        <v>2</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="B44" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="77" t="n">
-        <v>26</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Timing/Serialization</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="B45" s="46" t="n">
+        <v>48</v>
+      </c>
+      <c r="C45" s="75" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -20115,14 +20137,14 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Function/Class/Object</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0</v>
+          <t>Assignment/Initialization</t>
+        </is>
+      </c>
+      <c r="B46" s="65" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" s="76" t="n">
+        <v>2</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -20133,11 +20155,11 @@
       <c r="F46" t="n">
         <v>0</v>
       </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
+      <c r="G46" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="77" t="n">
+        <v>1</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -20146,26 +20168,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Interface/O-O Messages</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>0</v>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="n">
+        <v>14</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
       </c>
-      <c r="D47" s="76" t="n">
+      <c r="D47" s="78" t="n">
+        <v>26</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="77" t="n">
         <v>1</v>
       </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
+      <c r="G47" s="77" t="n">
+        <v>1</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -20177,11 +20199,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Relationship</t>
-        </is>
-      </c>
-      <c r="B48" s="76" t="n">
-        <v>1</v>
+          <t>Timing/Serialization</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -20208,237 +20230,214 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>Function/Class/Object</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Interface/O-O Messages</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="B51" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
         <is>
           <t>Agreement Rate</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
+      <c r="B53" s="1" t="inlineStr">
         <is>
           <t>76/106</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>71.7%</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>Mockito</t>
         </is>
       </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
+      <c r="B57" s="5" t="n"/>
+      <c r="C57" s="5" t="n"/>
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="5" t="n"/>
+      <c r="I57" s="5" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
         <is>
           <t>Scientific \ Few</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>Assignment/Initialization</t>
         </is>
       </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="E54" s="1" t="inlineStr">
+      <c r="D58" s="1" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="E58" s="1" t="inlineStr">
         <is>
           <t>Timing/Serialization</t>
         </is>
       </c>
-      <c r="F54" s="1" t="inlineStr">
+      <c r="F58" s="1" t="inlineStr">
         <is>
           <t>Function/Class/Object</t>
         </is>
       </c>
-      <c r="G54" s="1" t="inlineStr">
+      <c r="G58" s="1" t="inlineStr">
         <is>
           <t>Interface/O-O Messages</t>
         </is>
       </c>
-      <c r="H54" s="1" t="inlineStr">
+      <c r="H58" s="1" t="inlineStr">
         <is>
           <t>Relationship</t>
         </is>
       </c>
-      <c r="I54" s="1" t="inlineStr">
+      <c r="I58" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="B55" s="45" t="n">
-        <v>13</v>
-      </c>
-      <c r="C55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="70" t="n">
-        <v>3</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="60" t="n">
-        <v>1</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Assignment/Initialization</t>
-        </is>
-      </c>
-      <c r="B56" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="C56" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="60" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="B57" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="C57" s="60" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" s="78" t="n">
-        <v>11</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Timing/Serialization</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Function/Class/Object</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>0</v>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="B59" s="46" t="n">
+        <v>13</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -20449,14 +20448,14 @@
       <c r="E59" t="n">
         <v>0</v>
       </c>
-      <c r="F59" t="n">
-        <v>0</v>
+      <c r="F59" s="71" t="n">
+        <v>3</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
-      <c r="H59" t="n">
-        <v>0</v>
+      <c r="H59" s="61" t="n">
+        <v>1</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -20465,14 +20464,14 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Interface/O-O Messages</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" t="n">
-        <v>0</v>
+          <t>Assignment/Initialization</t>
+        </is>
+      </c>
+      <c r="B60" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C60" s="52" t="n">
+        <v>1</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -20480,8 +20479,8 @@
       <c r="E60" t="n">
         <v>0</v>
       </c>
-      <c r="F60" t="n">
-        <v>0</v>
+      <c r="F60" s="61" t="n">
+        <v>1</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -20496,17 +20495,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Relationship</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>0</v>
-      </c>
-      <c r="C61" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" t="n">
-        <v>0</v>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C61" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="79" t="n">
+        <v>11</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -20517,8 +20516,8 @@
       <c r="G61" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="51" t="n">
-        <v>1</v>
+      <c r="H61" t="n">
+        <v>0</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
@@ -20527,274 +20526,251 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>Timing/Serialization</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Function/Class/Object</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Interface/O-O Messages</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B62" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr">
-        <is>
-          <t>Agreement Rate</t>
-        </is>
-      </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>26/38</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>68.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
+          <t>Agreement Rate</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>26/38</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>68.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n"/>
+      <c r="C71" s="5" t="n"/>
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="n"/>
+      <c r="G71" s="5" t="n"/>
+      <c r="H71" s="5" t="n"/>
+      <c r="I71" s="5" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
           <t>Scientific \ Few</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="B72" s="1" t="inlineStr">
+        <is>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>Assignment/Initialization</t>
         </is>
       </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="E67" s="1" t="inlineStr">
+      <c r="D72" s="1" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="E72" s="1" t="inlineStr">
         <is>
           <t>Timing/Serialization</t>
         </is>
       </c>
-      <c r="F67" s="1" t="inlineStr">
+      <c r="F72" s="1" t="inlineStr">
         <is>
           <t>Function/Class/Object</t>
         </is>
       </c>
-      <c r="G67" s="1" t="inlineStr">
+      <c r="G72" s="1" t="inlineStr">
         <is>
           <t>Interface/O-O Messages</t>
         </is>
       </c>
-      <c r="H67" s="1" t="inlineStr">
+      <c r="H72" s="1" t="inlineStr">
         <is>
           <t>Relationship</t>
         </is>
       </c>
-      <c r="I67" s="1" t="inlineStr">
+      <c r="I72" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="B68" s="45" t="n">
-        <v>7</v>
-      </c>
-      <c r="C68" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" s="79" t="n">
-        <v>2</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Assignment/Initialization</t>
-        </is>
-      </c>
-      <c r="B69" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="C69" s="80" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="B70" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="C70" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" s="81" t="n">
-        <v>6</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Timing/Serialization</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Function/Class/Object</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>0</v>
-      </c>
-      <c r="C72" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Interface/O-O Messages</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>0</v>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="B73" s="46" t="n">
+        <v>7</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
-      <c r="D73" t="n">
-        <v>0</v>
+      <c r="D73" s="80" t="n">
+        <v>2</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -20815,14 +20791,14 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Relationship</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>0</v>
-      </c>
-      <c r="C74" t="n">
-        <v>0</v>
+          <t>Assignment/Initialization</t>
+        </is>
+      </c>
+      <c r="B74" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" s="81" t="n">
+        <v>1</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -20846,46 +20822,201 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="82" t="n">
+        <v>6</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Timing/Serialization</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Function/Class/Object</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Interface/O-O Messages</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B75" t="n">
-        <v>0</v>
-      </c>
-      <c r="C75" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr">
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
         <is>
           <t>Agreement Rate</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
+      <c r="B81" s="1" t="inlineStr">
         <is>
           <t>14/26</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>53.8%</t>
         </is>
@@ -20902,7 +21033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -20922,6 +21053,14 @@
           <t>All Projects</t>
         </is>
       </c>
+      <c r="B1" s="5" t="n"/>
+      <c r="C1" s="5" t="n"/>
+      <c r="D1" s="5" t="n"/>
+      <c r="E1" s="5" t="n"/>
+      <c r="F1" s="5" t="n"/>
+      <c r="G1" s="5" t="n"/>
+      <c r="H1" s="5" t="n"/>
+      <c r="I1" s="5" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -20976,13 +21115,13 @@
           <t>Algorithm/Method</t>
         </is>
       </c>
-      <c r="B3" s="45" t="n">
+      <c r="B3" s="46" t="n">
         <v>90</v>
       </c>
-      <c r="C3" s="82" t="n">
+      <c r="C3" s="83" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="52" t="n">
+      <c r="D3" s="53" t="n">
         <v>4</v>
       </c>
       <c r="E3" t="n">
@@ -21007,13 +21146,13 @@
           <t>Assignment/Initialization</t>
         </is>
       </c>
-      <c r="B4" s="83" t="n">
+      <c r="B4" s="84" t="n">
         <v>9</v>
       </c>
-      <c r="C4" s="84" t="n">
+      <c r="C4" s="85" t="n">
         <v>19</v>
       </c>
-      <c r="D4" s="82" t="n">
+      <c r="D4" s="83" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
@@ -21025,7 +21164,7 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="82" t="n">
+      <c r="H4" s="83" t="n">
         <v>2</v>
       </c>
       <c r="I4" t="n">
@@ -21041,10 +21180,10 @@
       <c r="B5" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="C5" s="85" t="n">
+      <c r="C5" s="86" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="86" t="n">
+      <c r="D5" s="87" t="n">
         <v>84</v>
       </c>
       <c r="E5" t="n">
@@ -21053,7 +21192,7 @@
       <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="82" t="n">
+      <c r="G5" s="83" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="n">
@@ -21100,7 +21239,7 @@
           <t>Function/Class/Object</t>
         </is>
       </c>
-      <c r="B7" s="85" t="n">
+      <c r="B7" s="86" t="n">
         <v>3</v>
       </c>
       <c r="C7" t="n">
@@ -21131,7 +21270,7 @@
           <t>Interface/O-O Messages</t>
         </is>
       </c>
-      <c r="B8" s="85" t="n">
+      <c r="B8" s="86" t="n">
         <v>3</v>
       </c>
       <c r="C8" t="n">
@@ -21146,7 +21285,7 @@
       <c r="F8" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="87" t="n">
+      <c r="G8" s="88" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="n">
@@ -21162,13 +21301,13 @@
           <t>Relationship</t>
         </is>
       </c>
-      <c r="B9" s="85" t="n">
+      <c r="B9" s="86" t="n">
         <v>3</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="85" t="n">
+      <c r="D9" s="86" t="n">
         <v>3</v>
       </c>
       <c r="E9" t="n">
@@ -21180,7 +21319,7 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="87" t="n">
+      <c r="H9" s="88" t="n">
         <v>2</v>
       </c>
       <c r="I9" t="n">
@@ -21218,119 +21357,96 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>Agreement Rate</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>197/257</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>76.7%</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Chart</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Scientific \ Few</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>Assignment/Initialization</t>
         </is>
       </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
         <is>
           <t>Timing/Serialization</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="F16" s="1" t="inlineStr">
         <is>
           <t>Function/Class/Object</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>Interface/O-O Messages</t>
         </is>
       </c>
-      <c r="H15" s="1" t="inlineStr">
+      <c r="H16" s="1" t="inlineStr">
         <is>
           <t>Relationship</t>
         </is>
       </c>
-      <c r="I15" s="1" t="inlineStr">
+      <c r="I16" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="B16" s="88" t="n">
-        <v>4</v>
-      </c>
-      <c r="C16" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Assignment/Initialization</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="n">
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="B17" s="89" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" s="18" t="n">
         <v>1</v>
-      </c>
-      <c r="C17" s="88" t="n">
-        <v>4</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -21354,17 +21470,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C18" s="17" t="n">
+          <t>Assignment/Initialization</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="45" t="n">
-        <v>11</v>
+      <c r="C18" s="89" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -21385,17 +21501,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Timing/Serialization</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="46" t="n">
+        <v>11</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -21416,11 +21532,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Function/Class/Object</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="n">
-        <v>1</v>
+          <t>Timing/Serialization</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -21447,11 +21563,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Interface/O-O Messages</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
+          <t>Function/Class/Object</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -21478,7 +21594,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Interface/O-O Messages</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -21509,31 +21625,62 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21554,136 +21701,82 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Lang</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>Scientific \ Few</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>Assignment/Initialization</t>
         </is>
       </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="E28" s="1" t="inlineStr">
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
         <is>
           <t>Timing/Serialization</t>
         </is>
       </c>
-      <c r="F28" s="1" t="inlineStr">
+      <c r="F30" s="1" t="inlineStr">
         <is>
           <t>Function/Class/Object</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
+      <c r="G30" s="1" t="inlineStr">
         <is>
           <t>Interface/O-O Messages</t>
         </is>
       </c>
-      <c r="H28" s="1" t="inlineStr">
+      <c r="H30" s="1" t="inlineStr">
         <is>
           <t>Relationship</t>
         </is>
       </c>
-      <c r="I28" s="1" t="inlineStr">
+      <c r="I30" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="B29" s="89" t="n">
-        <v>21</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Assignment/Initialization</t>
-        </is>
-      </c>
-      <c r="B30" s="85" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="75" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="85" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="85" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="n">
-        <v>8</v>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="B31" s="90" t="n">
+        <v>21</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="45" t="n">
-        <v>25</v>
+      <c r="D31" t="n">
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -21704,17 +21797,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Timing/Serialization</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
+          <t>Assignment/Initialization</t>
+        </is>
+      </c>
+      <c r="B32" s="86" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="86" t="n">
+        <v>1</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -21725,8 +21818,8 @@
       <c r="G32" t="n">
         <v>0</v>
       </c>
-      <c r="H32" t="n">
-        <v>0</v>
+      <c r="H32" s="86" t="n">
+        <v>1</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -21735,17 +21828,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Function/Class/Object</t>
-        </is>
-      </c>
-      <c r="B33" s="85" t="n">
-        <v>1</v>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
-      <c r="D33" t="n">
-        <v>0</v>
+      <c r="D33" s="46" t="n">
+        <v>25</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -21766,7 +21859,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Interface/O-O Messages</t>
+          <t>Timing/Serialization</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -21784,8 +21877,8 @@
       <c r="F34" t="n">
         <v>0</v>
       </c>
-      <c r="G34" s="75" t="n">
-        <v>1</v>
+      <c r="G34" t="n">
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -21797,10 +21890,10 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Relationship</t>
-        </is>
-      </c>
-      <c r="B35" s="85" t="n">
+          <t>Function/Class/Object</t>
+        </is>
+      </c>
+      <c r="B35" s="86" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
@@ -21828,212 +21921,189 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Interface/O-O Messages</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="B37" s="86" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
         <is>
           <t>Agreement Rate</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
+      <c r="B39" s="1" t="inlineStr">
         <is>
           <t>48/61</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>78.7%</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
         <is>
           <t>Scientific \ Few</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>Assignment/Initialization</t>
         </is>
       </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="inlineStr">
         <is>
           <t>Timing/Serialization</t>
         </is>
       </c>
-      <c r="F41" s="1" t="inlineStr">
+      <c r="F44" s="1" t="inlineStr">
         <is>
           <t>Function/Class/Object</t>
         </is>
       </c>
-      <c r="G41" s="1" t="inlineStr">
+      <c r="G44" s="1" t="inlineStr">
         <is>
           <t>Interface/O-O Messages</t>
         </is>
       </c>
-      <c r="H41" s="1" t="inlineStr">
+      <c r="H44" s="1" t="inlineStr">
         <is>
           <t>Relationship</t>
         </is>
       </c>
-      <c r="I41" s="1" t="inlineStr">
+      <c r="I44" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="B42" s="45" t="n">
-        <v>41</v>
-      </c>
-      <c r="C42" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="90" t="n">
-        <v>4</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Assignment/Initialization</t>
-        </is>
-      </c>
-      <c r="B43" s="91" t="n">
-        <v>5</v>
-      </c>
-      <c r="C43" s="92" t="n">
-        <v>9</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="B44" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="C44" s="79" t="n">
-        <v>2</v>
-      </c>
-      <c r="D44" s="93" t="n">
-        <v>29</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Timing/Serialization</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="B45" s="46" t="n">
+        <v>41</v>
+      </c>
+      <c r="C45" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="91" t="n">
+        <v>4</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -22054,14 +22124,14 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Function/Class/Object</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0</v>
+          <t>Assignment/Initialization</t>
+        </is>
+      </c>
+      <c r="B46" s="92" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" s="93" t="n">
+        <v>9</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -22085,17 +22155,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Interface/O-O Messages</t>
-        </is>
-      </c>
-      <c r="B47" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0</v>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C47" s="80" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" s="94" t="n">
+        <v>29</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -22103,8 +22173,8 @@
       <c r="F47" t="n">
         <v>0</v>
       </c>
-      <c r="G47" t="n">
-        <v>0</v>
+      <c r="G47" s="64" t="n">
+        <v>1</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -22116,11 +22186,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Relationship</t>
-        </is>
-      </c>
-      <c r="B48" s="63" t="n">
-        <v>1</v>
+          <t>Timing/Serialization</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -22137,8 +22207,8 @@
       <c r="G48" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="87" t="n">
-        <v>1</v>
+      <c r="H48" t="n">
+        <v>0</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -22147,237 +22217,214 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>Function/Class/Object</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Interface/O-O Messages</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="B51" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="88" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
         <is>
           <t>Agreement Rate</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
+      <c r="B53" s="1" t="inlineStr">
         <is>
           <t>80/106</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>75.5%</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>Mockito</t>
         </is>
       </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
+      <c r="B57" s="5" t="n"/>
+      <c r="C57" s="5" t="n"/>
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="5" t="n"/>
+      <c r="I57" s="5" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
         <is>
           <t>Scientific \ Few</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>Assignment/Initialization</t>
         </is>
       </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="E54" s="1" t="inlineStr">
+      <c r="D58" s="1" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="E58" s="1" t="inlineStr">
         <is>
           <t>Timing/Serialization</t>
         </is>
       </c>
-      <c r="F54" s="1" t="inlineStr">
+      <c r="F58" s="1" t="inlineStr">
         <is>
           <t>Function/Class/Object</t>
         </is>
       </c>
-      <c r="G54" s="1" t="inlineStr">
+      <c r="G58" s="1" t="inlineStr">
         <is>
           <t>Interface/O-O Messages</t>
         </is>
       </c>
-      <c r="H54" s="1" t="inlineStr">
+      <c r="H58" s="1" t="inlineStr">
         <is>
           <t>Relationship</t>
         </is>
       </c>
-      <c r="I54" s="1" t="inlineStr">
+      <c r="I58" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="B55" s="45" t="n">
-        <v>14</v>
-      </c>
-      <c r="C55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Assignment/Initialization</t>
-        </is>
-      </c>
-      <c r="B56" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C56" s="80" t="n">
-        <v>2</v>
-      </c>
-      <c r="D56" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>0</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="94" t="n">
-        <v>11</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Timing/Serialization</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Function/Class/Object</t>
-        </is>
-      </c>
-      <c r="B59" s="48" t="n">
-        <v>1</v>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="B59" s="46" t="n">
+        <v>14</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -22404,17 +22451,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Interface/O-O Messages</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" t="n">
-        <v>0</v>
+          <t>Assignment/Initialization</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C60" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" s="49" t="n">
+        <v>1</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
@@ -22422,11 +22469,11 @@
       <c r="F60" t="n">
         <v>0</v>
       </c>
-      <c r="G60" s="95" t="n">
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="49" t="n">
         <v>1</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
@@ -22435,29 +22482,29 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Relationship</t>
-        </is>
-      </c>
-      <c r="B61" s="48" t="n">
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="95" t="n">
+        <v>11</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="C61" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="95" t="n">
-        <v>1</v>
+      <c r="H61" t="n">
+        <v>0</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
@@ -22466,268 +22513,245 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>Timing/Serialization</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Function/Class/Object</t>
+        </is>
+      </c>
+      <c r="B63" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Interface/O-O Messages</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="B65" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="96" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B62" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr">
-        <is>
-          <t>Agreement Rate</t>
-        </is>
-      </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>29/38</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>76.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
+          <t>Agreement Rate</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>29/38</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>76.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n"/>
+      <c r="C71" s="5" t="n"/>
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="n"/>
+      <c r="G71" s="5" t="n"/>
+      <c r="H71" s="5" t="n"/>
+      <c r="I71" s="5" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
           <t>Scientific \ Few</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="B72" s="1" t="inlineStr">
+        <is>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>Assignment/Initialization</t>
         </is>
       </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="E67" s="1" t="inlineStr">
+      <c r="D72" s="1" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="E72" s="1" t="inlineStr">
         <is>
           <t>Timing/Serialization</t>
         </is>
       </c>
-      <c r="F67" s="1" t="inlineStr">
+      <c r="F72" s="1" t="inlineStr">
         <is>
           <t>Function/Class/Object</t>
         </is>
       </c>
-      <c r="G67" s="1" t="inlineStr">
+      <c r="G72" s="1" t="inlineStr">
         <is>
           <t>Interface/O-O Messages</t>
         </is>
       </c>
-      <c r="H67" s="1" t="inlineStr">
+      <c r="H72" s="1" t="inlineStr">
         <is>
           <t>Relationship</t>
         </is>
       </c>
-      <c r="I67" s="1" t="inlineStr">
+      <c r="I72" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Algorithm/Method</t>
-        </is>
-      </c>
-      <c r="B68" s="45" t="n">
-        <v>10</v>
-      </c>
-      <c r="C68" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Assignment/Initialization</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>0</v>
-      </c>
-      <c r="C69" s="96" t="n">
-        <v>3</v>
-      </c>
-      <c r="D69" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="B70" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="C70" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" s="38" t="n">
-        <v>8</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Timing/Serialization</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Function/Class/Object</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>0</v>
-      </c>
-      <c r="C72" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Interface/O-O Messages</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>0</v>
+          <t>Algorithm/Method</t>
+        </is>
+      </c>
+      <c r="B73" s="46" t="n">
+        <v>10</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -22754,17 +22778,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Assignment/Initialization</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>0</v>
       </c>
-      <c r="C74" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" s="60" t="n">
-        <v>1</v>
+      <c r="C74" s="97" t="n">
+        <v>3</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -22785,46 +22809,201 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Timing/Serialization</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Function/Class/Object</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Interface/O-O Messages</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B75" t="n">
-        <v>0</v>
-      </c>
-      <c r="C75" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr">
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
         <is>
           <t>Agreement Rate</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
+      <c r="B81" s="1" t="inlineStr">
         <is>
           <t>21/26</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>80.8%</t>
         </is>
